--- a/inventario_caixas_organizacao.xlsx
+++ b/inventario_caixas_organizacao.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2322c2e9e4f541f/Documentos/Casa/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{90DC00CF-4A85-4B33-AC26-97F154AEDC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D075220C-B121-4532-9DF7-97251CD9B486}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C218CEEC-C0C5-47C9-AA8E-EEAB45F3FE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5520" yWindow="348" windowWidth="15000" windowHeight="10176" tabRatio="690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventário de Caixas" sheetId="1" r:id="rId1"/>
     <sheet name="Configurações" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
   <si>
     <t>Caixa</t>
   </si>
@@ -148,6 +148,21 @@
   </si>
   <si>
     <t>corte</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Ponteiras</t>
+  </si>
+  <si>
+    <t>Várias medidas</t>
+  </si>
+  <si>
+    <t>Consumíveis (Ponteiras, Abraç, etc)</t>
+  </si>
+  <si>
+    <t>Abraçadeiras</t>
   </si>
 </sst>
 </file>
@@ -949,7 +964,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -967,26 +982,54 @@
         <v>36</v>
       </c>
       <c r="G10" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="2"/>
+      <c r="A11" s="2">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="2"/>
+      <c r="A12" s="2">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
@@ -1196,7 +1239,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Entrada Inválida" error="Valor não está na lista" promptTitle="Categoria" prompt="Selecione uma categoria da lista" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
-            <xm:f>Configurações!$A$2:$A$11</xm:f>
+            <xm:f>Configurações!$A$2:$A$12</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D210</xm:sqref>
         </x14:dataValidation>
@@ -1208,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.6640625" bestFit="1" customWidth="1"/>
@@ -1266,11 +1309,16 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>33</v>
       </c>
     </row>
